--- a/IEDC_Classification_fill/manual_insert/IEDC_99_NZIA_components.xlsx
+++ b/IEDC_Classification_fill/manual_insert/IEDC_99_NZIA_components.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C5E33C0-8FB7-40C9-9FA9-2B184F7218E3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F382952C-0332-4C6A-BEE3-511FFDB9138D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20922" windowHeight="8796" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Definition" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="112">
   <si>
     <t>Column</t>
   </si>
@@ -218,29 +218,152 @@
     <t>PV grade polysilicon</t>
   </si>
   <si>
-    <t>Solar PV systems</t>
-  </si>
-  <si>
     <t>attribute5_anc</t>
   </si>
   <si>
-    <t>Photovoltaic (PV) technologies</t>
-  </si>
-  <si>
-    <t>Solar technologies</t>
-  </si>
-  <si>
-    <t>PV grade silicon ingots or equivalent</t>
-  </si>
-  <si>
-    <t>Here, the term ‘equivalent’ refers to similar steps or key enabling technologies needed for thin-film, organic, tandem or other PV technologies.</t>
+    <t>floater</t>
+  </si>
+  <si>
+    <t>foundation</t>
+  </si>
+  <si>
+    <t>permanent magnet</t>
+  </si>
+  <si>
+    <t>drivetrain (including generator)</t>
+  </si>
+  <si>
+    <t>main yaw and pitch bearings</t>
+  </si>
+  <si>
+    <t>rotor hub</t>
+  </si>
+  <si>
+    <t>PV tracker and its specific mounting structure</t>
+  </si>
+  <si>
+    <t>PV inverter</t>
+  </si>
+  <si>
+    <t>PV module</t>
+  </si>
+  <si>
+    <t>PV cell solar glass</t>
+  </si>
+  <si>
+    <t>PV wafer</t>
+  </si>
+  <si>
+    <t>PV grade silicon ingot</t>
+  </si>
+  <si>
+    <t>battery thermal management systems (BTMS)</t>
+  </si>
+  <si>
+    <t>battery management system (BMS)</t>
+  </si>
+  <si>
+    <t>current collector</t>
+  </si>
+  <si>
+    <t>electrolyte</t>
+  </si>
+  <si>
+    <t>anode active material</t>
+  </si>
+  <si>
+    <t>cathode active material</t>
+  </si>
+  <si>
+    <t>battery cell</t>
+  </si>
+  <si>
+    <t>battery module</t>
+  </si>
+  <si>
+    <t>battery pack</t>
+  </si>
+  <si>
+    <t>nacelle</t>
+  </si>
+  <si>
+    <t>generator</t>
+  </si>
+  <si>
+    <t>gearbox</t>
+  </si>
+  <si>
+    <t>blade</t>
+  </si>
+  <si>
+    <t>tower</t>
+  </si>
+  <si>
+    <t>bipolar plate</t>
+  </si>
+  <si>
+    <t>end plate</t>
+  </si>
+  <si>
+    <t>membrane electrode assembly</t>
+  </si>
+  <si>
+    <t>catalyst-coated membrane</t>
+  </si>
+  <si>
+    <t>porous transport layer</t>
+  </si>
+  <si>
+    <t>gas diffusion layer</t>
+  </si>
+  <si>
+    <t>gasket</t>
+  </si>
+  <si>
+    <t>sealing</t>
+  </si>
+  <si>
+    <t>interconnector</t>
+  </si>
+  <si>
+    <t>mesh</t>
+  </si>
+  <si>
+    <t>stack</t>
+  </si>
+  <si>
+    <t>electrode</t>
+  </si>
+  <si>
+    <t>battery technologies</t>
+  </si>
+  <si>
+    <t>photovoltaic (PV) technologies</t>
+  </si>
+  <si>
+    <t>wind turbine technologies</t>
+  </si>
+  <si>
+    <t>electrolyzer technologies</t>
+  </si>
+  <si>
+    <t>separator, battery</t>
+  </si>
+  <si>
+    <t>separator, electrolyzer</t>
+  </si>
+  <si>
+    <t>original label: 'separator', added specification to avoid label conflict and confusion with separator for batteries.</t>
+  </si>
+  <si>
+    <t>original label: 'separator', added specification to avoid label conflict and confusion with separator for electrolysers.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -266,6 +389,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -304,20 +433,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -604,7 +726,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="18.83984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.578125" customWidth="1"/>
+    <col min="2" max="2" width="29.47265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -622,7 +744,7 @@
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="2">
         <v>99</v>
       </c>
       <c r="C2" s="2"/>
@@ -640,7 +762,7 @@
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -651,7 +773,7 @@
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C5" s="2"/>
@@ -669,7 +791,7 @@
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="2"/>
@@ -678,7 +800,7 @@
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="2"/>
@@ -696,7 +818,7 @@
       <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C10" s="2"/>
@@ -727,7 +849,7 @@
       <c r="A13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="3"/>
+      <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -737,7 +859,7 @@
       <c r="B14" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>61</v>
       </c>
     </row>
@@ -745,21 +867,21 @@
       <c r="A15" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="3"/>
+      <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="3"/>
+      <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="3"/>
+      <c r="B17" s="2"/>
       <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -789,68 +911,68 @@
       <c r="A22" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="3"/>
+      <c r="B22" s="2"/>
       <c r="C22" s="2"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="3"/>
+      <c r="B23" s="2"/>
       <c r="C23" s="2"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="3"/>
+      <c r="B24" s="2"/>
       <c r="C24" s="2"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="3"/>
+      <c r="B25" s="2"/>
       <c r="C25" s="2"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="3"/>
+      <c r="B26" s="2"/>
       <c r="C26" s="2"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="3"/>
+      <c r="B27" s="2"/>
       <c r="C27" s="2"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="3"/>
+      <c r="B28" s="2"/>
       <c r="C28" s="2"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="2"/>
-      <c r="B29" s="3"/>
+      <c r="B29" s="2"/>
       <c r="C29" s="2"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="3"/>
+      <c r="B30" s="2"/>
       <c r="C30" s="2"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C31" s="2"/>
@@ -859,7 +981,7 @@
       <c r="A32" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B32" s="4">
         <v>45847</v>
       </c>
       <c r="C32" s="2"/>
@@ -868,7 +990,7 @@
       <c r="A33" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C33" s="2"/>
@@ -899,54 +1021,54 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:T60"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.05078125" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:T42"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="3" width="8.578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="8.47265625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="20.41796875" customWidth="1"/>
-    <col min="9" max="9" width="10.734375" customWidth="1"/>
-    <col min="10" max="10" width="18.15625" customWidth="1"/>
-    <col min="11" max="11" width="24.7890625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.05078125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36.3125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.68359375" customWidth="1"/>
+    <col min="10" max="10" width="24.68359375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.83984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="J1" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="K1" s="11" t="s">
+      <c r="J1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="1" t="s">
         <v>46</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -985,16 +1107,10 @@
         <v>63</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="J2" t="s">
-        <v>65</v>
-      </c>
-      <c r="K2" t="s">
-        <v>67</v>
-      </c>
-      <c r="L2" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.55000000000000004">
@@ -1004,23 +1120,14 @@
       <c r="B3">
         <v>99</v>
       </c>
-      <c r="D3" t="s">
-        <v>70</v>
-      </c>
       <c r="E3" t="s">
         <v>63</v>
       </c>
       <c r="F3" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="J3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K3" t="s">
-        <v>67</v>
-      </c>
-      <c r="L3" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.55000000000000004">
@@ -1030,7 +1137,15 @@
       <c r="B4">
         <v>99</v>
       </c>
-      <c r="F4" s="8"/>
+      <c r="E4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" t="s">
+        <v>84</v>
+      </c>
+      <c r="J4" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
@@ -1039,6 +1154,15 @@
       <c r="B5">
         <v>99</v>
       </c>
+      <c r="E5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" t="s">
+        <v>83</v>
+      </c>
+      <c r="J5" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
@@ -1047,6 +1171,15 @@
       <c r="B6">
         <v>99</v>
       </c>
+      <c r="E6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" t="s">
+        <v>82</v>
+      </c>
+      <c r="J6" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
@@ -1055,74 +1188,619 @@
       <c r="B7">
         <v>99</v>
       </c>
-    </row>
-    <row r="39" spans="6:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="F39" s="9"/>
-    </row>
-    <row r="40" spans="6:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="F40" s="9"/>
-    </row>
-    <row r="41" spans="6:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="F41" s="9"/>
-    </row>
-    <row r="42" spans="6:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="F42" s="9"/>
-    </row>
-    <row r="43" spans="6:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="F43" s="9"/>
-    </row>
-    <row r="44" spans="6:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="F44" s="9"/>
-    </row>
-    <row r="45" spans="6:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="F45" s="9"/>
-    </row>
-    <row r="46" spans="6:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="F46" s="10"/>
-    </row>
-    <row r="47" spans="6:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="F47" s="9"/>
-    </row>
-    <row r="48" spans="6:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="F48" s="10"/>
-    </row>
-    <row r="49" spans="6:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="F49" s="10"/>
-    </row>
-    <row r="50" spans="6:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="F50" s="10"/>
-    </row>
-    <row r="51" spans="6:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="F51" s="10"/>
-    </row>
-    <row r="52" spans="6:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="F52" s="10"/>
-    </row>
-    <row r="53" spans="6:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="F53" s="10"/>
-    </row>
-    <row r="54" spans="6:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="F54" s="10"/>
-    </row>
-    <row r="55" spans="6:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="F55" s="10"/>
-    </row>
-    <row r="56" spans="6:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="F56" s="10"/>
-    </row>
-    <row r="57" spans="6:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="F57" s="10"/>
-    </row>
-    <row r="58" spans="6:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="F58" s="10"/>
-    </row>
-    <row r="59" spans="6:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="F59" s="10"/>
-    </row>
-    <row r="60" spans="6:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="F60" s="10"/>
+      <c r="E7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" t="s">
+        <v>81</v>
+      </c>
+      <c r="J7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>99</v>
+      </c>
+      <c r="D8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" t="s">
+        <v>108</v>
+      </c>
+      <c r="J8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>99</v>
+      </c>
+      <c r="E9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" t="s">
+        <v>80</v>
+      </c>
+      <c r="J9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>99</v>
+      </c>
+      <c r="E10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" t="s">
+        <v>79</v>
+      </c>
+      <c r="J10" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>99</v>
+      </c>
+      <c r="E11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" t="s">
+        <v>78</v>
+      </c>
+      <c r="J11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>99</v>
+      </c>
+      <c r="E12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" t="s">
+        <v>64</v>
+      </c>
+      <c r="J12" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>99</v>
+      </c>
+      <c r="E13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" t="s">
+        <v>77</v>
+      </c>
+      <c r="J13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>99</v>
+      </c>
+      <c r="E14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" t="s">
+        <v>76</v>
+      </c>
+      <c r="J14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>99</v>
+      </c>
+      <c r="E15" t="s">
+        <v>63</v>
+      </c>
+      <c r="F15" t="s">
+        <v>75</v>
+      </c>
+      <c r="J15" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>99</v>
+      </c>
+      <c r="E16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F16" t="s">
+        <v>74</v>
+      </c>
+      <c r="J16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>99</v>
+      </c>
+      <c r="E17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F17" t="s">
+        <v>73</v>
+      </c>
+      <c r="J17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>99</v>
+      </c>
+      <c r="E18" t="s">
+        <v>63</v>
+      </c>
+      <c r="F18" t="s">
+        <v>72</v>
+      </c>
+      <c r="J18" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>99</v>
+      </c>
+      <c r="E19" t="s">
+        <v>63</v>
+      </c>
+      <c r="F19" t="s">
+        <v>71</v>
+      </c>
+      <c r="J19" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>99</v>
+      </c>
+      <c r="E20" t="s">
+        <v>63</v>
+      </c>
+      <c r="F20" t="s">
+        <v>70</v>
+      </c>
+      <c r="J20" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>99</v>
+      </c>
+      <c r="E21" t="s">
+        <v>63</v>
+      </c>
+      <c r="F21" t="s">
+        <v>69</v>
+      </c>
+      <c r="J21" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>99</v>
+      </c>
+      <c r="E22" t="s">
+        <v>63</v>
+      </c>
+      <c r="F22" t="s">
+        <v>68</v>
+      </c>
+      <c r="J22" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>99</v>
+      </c>
+      <c r="E23" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" t="s">
+        <v>67</v>
+      </c>
+      <c r="J23" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>99</v>
+      </c>
+      <c r="E24" t="s">
+        <v>63</v>
+      </c>
+      <c r="F24" t="s">
+        <v>66</v>
+      </c>
+      <c r="J24" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>99</v>
+      </c>
+      <c r="E25" t="s">
+        <v>63</v>
+      </c>
+      <c r="F25" t="s">
+        <v>87</v>
+      </c>
+      <c r="J25" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>99</v>
+      </c>
+      <c r="E26" t="s">
+        <v>63</v>
+      </c>
+      <c r="F26" t="s">
+        <v>88</v>
+      </c>
+      <c r="J26" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>99</v>
+      </c>
+      <c r="E27" t="s">
+        <v>63</v>
+      </c>
+      <c r="F27" t="s">
+        <v>89</v>
+      </c>
+      <c r="J27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>99</v>
+      </c>
+      <c r="E28" t="s">
+        <v>63</v>
+      </c>
+      <c r="F28" t="s">
+        <v>90</v>
+      </c>
+      <c r="J28" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>99</v>
+      </c>
+      <c r="E29" t="s">
+        <v>63</v>
+      </c>
+      <c r="F29" t="s">
+        <v>91</v>
+      </c>
+      <c r="J29" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>99</v>
+      </c>
+      <c r="D30" t="s">
+        <v>110</v>
+      </c>
+      <c r="E30" t="s">
+        <v>63</v>
+      </c>
+      <c r="F30" t="s">
+        <v>109</v>
+      </c>
+      <c r="J30" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>99</v>
+      </c>
+      <c r="E31" t="s">
+        <v>63</v>
+      </c>
+      <c r="F31" t="s">
+        <v>92</v>
+      </c>
+      <c r="J31" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>99</v>
+      </c>
+      <c r="E32" t="s">
+        <v>63</v>
+      </c>
+      <c r="F32" t="s">
+        <v>93</v>
+      </c>
+      <c r="J32" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>99</v>
+      </c>
+      <c r="E33" t="s">
+        <v>63</v>
+      </c>
+      <c r="F33" t="s">
+        <v>94</v>
+      </c>
+      <c r="J33" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>99</v>
+      </c>
+      <c r="E34" t="s">
+        <v>63</v>
+      </c>
+      <c r="F34" t="s">
+        <v>95</v>
+      </c>
+      <c r="J34" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>99</v>
+      </c>
+      <c r="E35" t="s">
+        <v>63</v>
+      </c>
+      <c r="F35" t="s">
+        <v>96</v>
+      </c>
+      <c r="J35" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>99</v>
+      </c>
+      <c r="E36" t="s">
+        <v>63</v>
+      </c>
+      <c r="F36" t="s">
+        <v>97</v>
+      </c>
+      <c r="J36" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>99</v>
+      </c>
+      <c r="E37" t="s">
+        <v>63</v>
+      </c>
+      <c r="F37" t="s">
+        <v>98</v>
+      </c>
+      <c r="J37" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>99</v>
+      </c>
+      <c r="E38" t="s">
+        <v>63</v>
+      </c>
+      <c r="F38" t="s">
+        <v>99</v>
+      </c>
+      <c r="J38" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>99</v>
+      </c>
+      <c r="E39" t="s">
+        <v>63</v>
+      </c>
+      <c r="F39" t="s">
+        <v>100</v>
+      </c>
+      <c r="J39" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>99</v>
+      </c>
+      <c r="E40" t="s">
+        <v>63</v>
+      </c>
+      <c r="F40" t="s">
+        <v>101</v>
+      </c>
+      <c r="J40" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>99</v>
+      </c>
+      <c r="E41" t="s">
+        <v>63</v>
+      </c>
+      <c r="F41" t="s">
+        <v>102</v>
+      </c>
+      <c r="J41" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>99</v>
+      </c>
+      <c r="E42" t="s">
+        <v>63</v>
+      </c>
+      <c r="F42" t="s">
+        <v>103</v>
+      </c>
+      <c r="J42" t="s">
+        <v>107</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
